--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelDrivenRack1UJ.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_WheelDrivenRack1UJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6982BE-063B-4E5B-A5F0-224A8DFF270E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE73030-0923-4C45-8384-40C68F4761C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="2730" windowWidth="26910" windowHeight="12765" xr2:uid="{E5F5FC43-B986-4E29-966F-C8C2FD1E0A42}"/>
+    <workbookView xWindow="270" yWindow="1230" windowWidth="21600" windowHeight="13230" activeTab="1" xr2:uid="{E5F5FC43-B986-4E29-966F-C8C2FD1E0A42}"/>
   </bookViews>
   <sheets>
     <sheet name="WDrivenRack_1UJ_Achilles" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="41">
   <si>
     <t>It is included here so that this variant can be used with the test harness.</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>WheelDrivenRack1UJoint_Ch2_Achilles</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -247,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -294,12 +300,45 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{07716AD1-3E1E-463C-8691-28D31A0398FC}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -689,7 +728,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -832,137 +871,117 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="1:28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-0.46200000000000002</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.48907</v>
+        <v>22</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+      <c r="A10" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="B10" s="10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7">
-        <v>0.11558</v>
+        <v>4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-0.46200000000000002</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.48907</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="10" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="14">
-        <v>1</v>
+      <c r="H11" s="7">
+        <v>0.11558</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C12" s="10"/>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="18" t="s">
-        <v>17</v>
+      <c r="H12" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="11"/>
       <c r="B13" s="10" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C13" s="10"/>
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
+      <c r="H13" s="18" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="B14" s="10" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="8">
-        <v>0.17230999999999999</v>
+      <c r="H14" s="17">
+        <v>0.2</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -986,460 +1005,485 @@
       <c r="AB14" s="15"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="A15" s="11"/>
       <c r="B15" s="10" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="14">
-        <v>0.2</v>
-      </c>
+      <c r="H15" s="8">
+        <v>0.17230999999999999</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="13">
-        <v>7.7869999999999995E-2</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0.10644000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+      <c r="A17" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="B17" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
-        <f>0.01365</f>
-        <v>1.3650000000000001E-2</v>
+      <c r="F17" s="13">
+        <v>7.7869999999999995E-2</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0.10644000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>0.05</v>
+        <f>0.01365</f>
+        <v>1.3650000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="11"/>
       <c r="B19" s="10" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="12">
-        <f>H24*$H$25</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I19" s="12">
-        <f>I24*$H$25</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J19" s="12">
-        <f>J24*$H$25</f>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K19" s="12">
-        <f>K24*$H$25</f>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L19" s="12">
-        <f>L24*$H$25</f>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M19" s="12">
-        <f>M24*$H$25</f>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N19" s="12">
-        <f>N24*$H$25</f>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O19" s="12">
-        <f>O24*$H$25</f>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P19" s="12">
-        <f>P24*$H$25</f>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q19" s="12">
-        <f>Q24*$H$25</f>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R19" s="12">
-        <f>R24*$H$25</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="12">
-        <f>S24*$H$25</f>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T19" s="12">
-        <f>T24*$H$25</f>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U19" s="12">
-        <f>U24*$H$25</f>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V19" s="12">
-        <f>V24*$H$25</f>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W19" s="12">
-        <f>W24*$H$25</f>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X19" s="12">
-        <f>X24*$H$25</f>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y19" s="12">
-        <f>Y24*$H$25</f>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z19" s="12">
-        <f>Z24*$H$25</f>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA19" s="12">
-        <f>AA24*$H$25</f>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB19" s="12">
-        <f>AB24*$H$25</f>
-        <v>3.1415700000000002</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="B20" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="8">
-        <f>H19*$H$26*180/3.14159</f>
+      <c r="H20" s="12">
+        <f t="shared" ref="H20:AB20" si="0">H25*$H$26</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R20" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB20" s="12">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="8">
+        <f t="shared" ref="H21:AB21" si="1">H20*$H$27*180/3.14159</f>
         <v>-4.2893726928084193E-2</v>
       </c>
-      <c r="I20" s="8">
-        <f>I19*$H$26*180/3.14159</f>
+      <c r="I21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.8604354235275778E-2</v>
       </c>
-      <c r="J20" s="8">
-        <f>J19*$H$26*180/3.14159</f>
+      <c r="J21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.431498154246735E-2</v>
       </c>
-      <c r="K20" s="8">
-        <f>K19*$H$26*180/3.14159</f>
+      <c r="K21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.0025608849658939E-2</v>
       </c>
-      <c r="L20" s="8">
-        <f>L19*$H$26*180/3.14159</f>
+      <c r="L21" s="8">
+        <f t="shared" si="1"/>
         <v>-2.5736236156850518E-2</v>
       </c>
-      <c r="M20" s="8">
-        <f>M19*$H$26*180/3.14159</f>
+      <c r="M21" s="8">
+        <f t="shared" si="1"/>
         <v>-2.1446863464042096E-2</v>
       </c>
-      <c r="N20" s="8">
-        <f>N19*$H$26*180/3.14159</f>
+      <c r="N21" s="8">
+        <f t="shared" si="1"/>
         <v>-1.7157490771233675E-2</v>
       </c>
-      <c r="O20" s="8">
-        <f>O19*$H$26*180/3.14159</f>
+      <c r="O21" s="8">
+        <f t="shared" si="1"/>
         <v>-1.2868118078425259E-2</v>
       </c>
-      <c r="P20" s="8">
-        <f>P19*$H$26*180/3.14159</f>
+      <c r="P21" s="8">
+        <f t="shared" si="1"/>
         <v>-8.5787453856168375E-3</v>
       </c>
-      <c r="Q20" s="8">
-        <f>Q19*$H$26*180/3.14159</f>
+      <c r="Q21" s="8">
+        <f t="shared" si="1"/>
         <v>-4.2893726928084188E-3</v>
       </c>
-      <c r="R20" s="8">
-        <f>R19*$H$26*180/3.14159</f>
+      <c r="R21" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S20" s="8">
-        <f>S19*$H$26*180/3.14159</f>
+      <c r="S21" s="8">
+        <f t="shared" si="1"/>
         <v>4.2893726928084188E-3</v>
       </c>
-      <c r="T20" s="8">
-        <f>T19*$H$26*180/3.14159</f>
+      <c r="T21" s="8">
+        <f t="shared" si="1"/>
         <v>8.5787453856168375E-3</v>
       </c>
-      <c r="U20" s="8">
-        <f>U19*$H$26*180/3.14159</f>
+      <c r="U21" s="8">
+        <f t="shared" si="1"/>
         <v>1.2868118078425259E-2</v>
       </c>
-      <c r="V20" s="8">
-        <f>V19*$H$26*180/3.14159</f>
+      <c r="V21" s="8">
+        <f t="shared" si="1"/>
         <v>1.7157490771233675E-2</v>
       </c>
-      <c r="W20" s="8">
-        <f>W19*$H$26*180/3.14159</f>
+      <c r="W21" s="8">
+        <f t="shared" si="1"/>
         <v>2.1446863464042096E-2</v>
       </c>
-      <c r="X20" s="8">
-        <f>X19*$H$26*180/3.14159</f>
+      <c r="X21" s="8">
+        <f t="shared" si="1"/>
         <v>2.5736236156850518E-2</v>
       </c>
-      <c r="Y20" s="8">
-        <f>Y19*$H$26*180/3.14159</f>
+      <c r="Y21" s="8">
+        <f t="shared" si="1"/>
         <v>3.0025608849658939E-2</v>
       </c>
-      <c r="Z20" s="8">
-        <f>Z19*$H$26*180/3.14159</f>
+      <c r="Z21" s="8">
+        <f t="shared" si="1"/>
         <v>3.431498154246735E-2</v>
       </c>
-      <c r="AA20" s="8">
-        <f>AA19*$H$26*180/3.14159</f>
+      <c r="AA21" s="8">
+        <f t="shared" si="1"/>
         <v>3.8604354235275778E-2</v>
       </c>
-      <c r="AB20" s="8">
-        <f>AB19*$H$26*180/3.14159</f>
+      <c r="AB21" s="8">
+        <f t="shared" si="1"/>
         <v>4.2893726928084193E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J22" s="1">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K22" s="1">
-        <v>-0.2112</v>
-      </c>
-      <c r="L22" s="1">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.1462</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-0.1178</v>
-      </c>
-      <c r="O22" s="1">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P22" s="1">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T22" s="1">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U22" s="1">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0.1178</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>0.2112</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>0.3</v>
-      </c>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="1">
+      <c r="H23" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-0.2112</v>
+      </c>
+      <c r="L23" s="1">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-0.1462</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-0.1178</v>
+      </c>
+      <c r="O23" s="1">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P23" s="1">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T23" s="1">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U23" s="1">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0.1178</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0.2112</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="1">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="7">
-        <v>-180</v>
-      </c>
-      <c r="I24" s="1">
-        <v>-162</v>
-      </c>
-      <c r="J24" s="1">
-        <v>-144</v>
-      </c>
-      <c r="K24" s="1">
-        <v>-126</v>
-      </c>
-      <c r="L24" s="1">
-        <v>-108</v>
-      </c>
-      <c r="M24" s="1">
-        <v>-90</v>
-      </c>
-      <c r="N24" s="1">
-        <v>-72</v>
-      </c>
-      <c r="O24" s="1">
-        <v>-54</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-36</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>-18</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>18</v>
-      </c>
-      <c r="T24" s="1">
-        <v>36</v>
-      </c>
-      <c r="U24" s="1">
-        <v>54</v>
-      </c>
-      <c r="V24" s="1">
-        <v>72</v>
-      </c>
-      <c r="W24" s="1">
-        <v>90</v>
-      </c>
-      <c r="X24" s="1">
-        <v>108</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>126</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>144</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>162</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>180</v>
-      </c>
-    </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
-      <c r="H25" s="1">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="7">
+        <v>-180</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-162</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-144</v>
+      </c>
+      <c r="K25" s="1">
+        <v>-126</v>
+      </c>
+      <c r="L25" s="1">
+        <v>-108</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-90</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-72</v>
+      </c>
+      <c r="O25" s="1">
+        <v>-54</v>
+      </c>
+      <c r="P25" s="1">
+        <v>-36</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>-18</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>18</v>
+      </c>
+      <c r="T25" s="1">
+        <v>36</v>
+      </c>
+      <c r="U25" s="1">
+        <v>54</v>
+      </c>
+      <c r="V25" s="1">
+        <v>72</v>
+      </c>
+      <c r="W25" s="1">
+        <v>90</v>
+      </c>
+      <c r="X25" s="1">
+        <v>108</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>126</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>144</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>162</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="H26" s="1">
         <f>3.14157/180</f>
         <v>1.7453166666666669E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H26" s="1">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H27" s="1">
         <f>0.0002383</f>
         <v>2.3829999999999999E-4</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="H28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E31" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -1447,24 +1491,44 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A28:A29">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+  <conditionalFormatting sqref="A29:A30">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B20">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B21">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:B27">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+  <conditionalFormatting sqref="A25:B28">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E20">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="E5 E7 E9:E21">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1477,7 +1541,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -1621,137 +1685,117 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="1:28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6">
-        <v>-0.56000000000000005</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.47</v>
+        <v>22</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+      <c r="A10" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="B10" s="10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7">
-        <v>0.18</v>
+        <v>4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>-0.56000000000000005</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.47</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="10" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7">
-        <v>1</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C12" s="10"/>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="18" t="s">
-        <v>17</v>
+      <c r="H12" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="11"/>
       <c r="B13" s="10" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C13" s="10"/>
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
+      <c r="H13" s="18" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
+      <c r="A14" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="B14" s="10" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="8">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -1775,460 +1819,485 @@
       <c r="AB14" s="15"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="A15" s="11"/>
       <c r="B15" s="10" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="7">
-        <v>0.2</v>
-      </c>
+      <c r="H15" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="13">
-        <v>7.7869999999999995E-2</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0.10644000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
+      <c r="A17" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="B17" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="1">
-        <f>0.01365</f>
-        <v>1.3650000000000001E-2</v>
+      <c r="F17" s="13">
+        <v>7.7869999999999995E-2</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0.10644000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>0.05</v>
+        <f>0.01365</f>
+        <v>1.3650000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="11"/>
       <c r="B19" s="10" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="12">
-        <f>H24*$H$25</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I19" s="12">
-        <f>I24*$H$25</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J19" s="12">
-        <f>J24*$H$25</f>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K19" s="12">
-        <f>K24*$H$25</f>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L19" s="12">
-        <f>L24*$H$25</f>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M19" s="12">
-        <f>M24*$H$25</f>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N19" s="12">
-        <f>N24*$H$25</f>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O19" s="12">
-        <f>O24*$H$25</f>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P19" s="12">
-        <f>P24*$H$25</f>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q19" s="12">
-        <f>Q24*$H$25</f>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R19" s="12">
-        <f>R24*$H$25</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="12">
-        <f>S24*$H$25</f>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T19" s="12">
-        <f>T24*$H$25</f>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U19" s="12">
-        <f>U24*$H$25</f>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V19" s="12">
-        <f>V24*$H$25</f>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W19" s="12">
-        <f>W24*$H$25</f>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X19" s="12">
-        <f>X24*$H$25</f>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y19" s="12">
-        <f>Y24*$H$25</f>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z19" s="12">
-        <f>Z24*$H$25</f>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA19" s="12">
-        <f>AA24*$H$25</f>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB19" s="12">
-        <f>AB24*$H$25</f>
-        <v>3.1415700000000002</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
+      <c r="A20" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="B20" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="8">
-        <f>H19*$H$26*180/3.14159</f>
+      <c r="H20" s="12">
+        <f t="shared" ref="H20:AB20" si="0">H25*$H$26</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N20" s="12">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R20" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X20" s="12">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA20" s="12">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB20" s="12">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="8">
+        <f t="shared" ref="H21:AB21" si="1">H20*$H$27*180/3.14159</f>
         <v>-4.2893726928084193E-2</v>
       </c>
-      <c r="I20" s="8">
-        <f>I19*$H$26*180/3.14159</f>
+      <c r="I21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.8604354235275778E-2</v>
       </c>
-      <c r="J20" s="8">
-        <f>J19*$H$26*180/3.14159</f>
+      <c r="J21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.431498154246735E-2</v>
       </c>
-      <c r="K20" s="8">
-        <f>K19*$H$26*180/3.14159</f>
+      <c r="K21" s="8">
+        <f t="shared" si="1"/>
         <v>-3.0025608849658939E-2</v>
       </c>
-      <c r="L20" s="8">
-        <f>L19*$H$26*180/3.14159</f>
+      <c r="L21" s="8">
+        <f t="shared" si="1"/>
         <v>-2.5736236156850518E-2</v>
       </c>
-      <c r="M20" s="8">
-        <f>M19*$H$26*180/3.14159</f>
+      <c r="M21" s="8">
+        <f t="shared" si="1"/>
         <v>-2.1446863464042096E-2</v>
       </c>
-      <c r="N20" s="8">
-        <f>N19*$H$26*180/3.14159</f>
+      <c r="N21" s="8">
+        <f t="shared" si="1"/>
         <v>-1.7157490771233675E-2</v>
       </c>
-      <c r="O20" s="8">
-        <f>O19*$H$26*180/3.14159</f>
+      <c r="O21" s="8">
+        <f t="shared" si="1"/>
         <v>-1.2868118078425259E-2</v>
       </c>
-      <c r="P20" s="8">
-        <f>P19*$H$26*180/3.14159</f>
+      <c r="P21" s="8">
+        <f t="shared" si="1"/>
         <v>-8.5787453856168375E-3</v>
       </c>
-      <c r="Q20" s="8">
-        <f>Q19*$H$26*180/3.14159</f>
+      <c r="Q21" s="8">
+        <f t="shared" si="1"/>
         <v>-4.2893726928084188E-3</v>
       </c>
-      <c r="R20" s="8">
-        <f>R19*$H$26*180/3.14159</f>
+      <c r="R21" s="8">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S20" s="8">
-        <f>S19*$H$26*180/3.14159</f>
+      <c r="S21" s="8">
+        <f t="shared" si="1"/>
         <v>4.2893726928084188E-3</v>
       </c>
-      <c r="T20" s="8">
-        <f>T19*$H$26*180/3.14159</f>
+      <c r="T21" s="8">
+        <f t="shared" si="1"/>
         <v>8.5787453856168375E-3</v>
       </c>
-      <c r="U20" s="8">
-        <f>U19*$H$26*180/3.14159</f>
+      <c r="U21" s="8">
+        <f t="shared" si="1"/>
         <v>1.2868118078425259E-2</v>
       </c>
-      <c r="V20" s="8">
-        <f>V19*$H$26*180/3.14159</f>
+      <c r="V21" s="8">
+        <f t="shared" si="1"/>
         <v>1.7157490771233675E-2</v>
       </c>
-      <c r="W20" s="8">
-        <f>W19*$H$26*180/3.14159</f>
+      <c r="W21" s="8">
+        <f t="shared" si="1"/>
         <v>2.1446863464042096E-2</v>
       </c>
-      <c r="X20" s="8">
-        <f>X19*$H$26*180/3.14159</f>
+      <c r="X21" s="8">
+        <f t="shared" si="1"/>
         <v>2.5736236156850518E-2</v>
       </c>
-      <c r="Y20" s="8">
-        <f>Y19*$H$26*180/3.14159</f>
+      <c r="Y21" s="8">
+        <f t="shared" si="1"/>
         <v>3.0025608849658939E-2</v>
       </c>
-      <c r="Z20" s="8">
-        <f>Z19*$H$26*180/3.14159</f>
+      <c r="Z21" s="8">
+        <f t="shared" si="1"/>
         <v>3.431498154246735E-2</v>
       </c>
-      <c r="AA20" s="8">
-        <f>AA19*$H$26*180/3.14159</f>
+      <c r="AA21" s="8">
+        <f t="shared" si="1"/>
         <v>3.8604354235275778E-2</v>
       </c>
-      <c r="AB20" s="8">
-        <f>AB19*$H$26*180/3.14159</f>
+      <c r="AB21" s="8">
+        <f t="shared" si="1"/>
         <v>4.2893726928084193E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="I22" s="1">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J22" s="1">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K22" s="1">
-        <v>-0.2112</v>
-      </c>
-      <c r="L22" s="1">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M22" s="1">
-        <v>-0.1462</v>
-      </c>
-      <c r="N22" s="1">
-        <v>-0.1178</v>
-      </c>
-      <c r="O22" s="1">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P22" s="1">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T22" s="1">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U22" s="1">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0.1178</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>0.2112</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>0.3</v>
-      </c>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="1">
+      <c r="H23" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-0.2112</v>
+      </c>
+      <c r="L23" s="1">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M23" s="1">
+        <v>-0.1462</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-0.1178</v>
+      </c>
+      <c r="O23" s="1">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P23" s="1">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T23" s="1">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U23" s="1">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0.1178</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0.2112</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="1">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="7">
-        <v>-180</v>
-      </c>
-      <c r="I24" s="1">
-        <v>-162</v>
-      </c>
-      <c r="J24" s="1">
-        <v>-144</v>
-      </c>
-      <c r="K24" s="1">
-        <v>-126</v>
-      </c>
-      <c r="L24" s="1">
-        <v>-108</v>
-      </c>
-      <c r="M24" s="1">
-        <v>-90</v>
-      </c>
-      <c r="N24" s="1">
-        <v>-72</v>
-      </c>
-      <c r="O24" s="1">
-        <v>-54</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-36</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>-18</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>18</v>
-      </c>
-      <c r="T24" s="1">
-        <v>36</v>
-      </c>
-      <c r="U24" s="1">
-        <v>54</v>
-      </c>
-      <c r="V24" s="1">
-        <v>72</v>
-      </c>
-      <c r="W24" s="1">
-        <v>90</v>
-      </c>
-      <c r="X24" s="1">
-        <v>108</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>126</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>144</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>162</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>180</v>
-      </c>
-    </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
-      <c r="H25" s="1">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="7">
+        <v>-180</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-162</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-144</v>
+      </c>
+      <c r="K25" s="1">
+        <v>-126</v>
+      </c>
+      <c r="L25" s="1">
+        <v>-108</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-90</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-72</v>
+      </c>
+      <c r="O25" s="1">
+        <v>-54</v>
+      </c>
+      <c r="P25" s="1">
+        <v>-36</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>-18</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>18</v>
+      </c>
+      <c r="T25" s="1">
+        <v>36</v>
+      </c>
+      <c r="U25" s="1">
+        <v>54</v>
+      </c>
+      <c r="V25" s="1">
+        <v>72</v>
+      </c>
+      <c r="W25" s="1">
+        <v>90</v>
+      </c>
+      <c r="X25" s="1">
+        <v>108</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>126</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>144</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>162</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="H26" s="1">
         <f>3.14157/180</f>
         <v>1.7453166666666669E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H26" s="1">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H27" s="1">
         <f>0.0002383</f>
         <v>2.3829999999999999E-4</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-    </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B28" s="2"/>
-      <c r="H28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="E30" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="B30" s="2"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E31" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -2236,23 +2305,43 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="E32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A28:A29">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="A29:A30">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B20">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B21">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:B27">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="A25:B28">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E20">
+  <conditionalFormatting sqref="E5 E7 E9:E21">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
